--- a/output/pdf_financials_xlsx/SX.xlsx
+++ b/output/pdf_financials_xlsx/SX.xlsx
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>19.128927</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>11.610586</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>11.806859</v>
       </c>
     </row>
     <row r="93">
@@ -3388,7 +3388,11 @@
           <t>Reserves 14,18</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>19.128927</v>
       </c>

--- a/output/pdf_financials_xlsx/SX.xlsx
+++ b/output/pdf_financials_xlsx/SX.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1.874867</v>
+        <v>2.492876</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.107409</v>
+        <v>2.038625</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.797504</v>
+        <v>1.916631</v>
       </c>
     </row>
     <row r="8">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2.47595</v>
+        <v>3.093959</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.417383</v>
+        <v>2.348599</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.903224</v>
+        <v>2.022351</v>
       </c>
     </row>
     <row r="11">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.669392</v>
+        <v>-5.407362</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-8.239867</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-3.843283</v>
+        <v>-3.84263</v>
       </c>
     </row>
     <row r="21">
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.223629</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>-0.000653</v>
       </c>
     </row>
     <row r="22">
@@ -1464,13 +1464,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>4.225156</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.918389</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>4.331566</v>
       </c>
     </row>
     <row r="65">
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.467458</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.25235</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.295172</v>
       </c>
     </row>
     <row r="68">
@@ -2213,13 +2213,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.105582</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-1.42359</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.052858</v>
       </c>
     </row>
     <row r="112">
@@ -2280,10 +2280,10 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.238307</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.047594</v>
       </c>
     </row>
     <row r="116">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.105582</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-1.42359</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.052858</v>
       </c>
     </row>
     <row r="135">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.995521</v>
+        <v>-2.101103</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-2.838263</v>
+        <v>-4.261853</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>0.801309</v>
+        <v>0.748451</v>
       </c>
     </row>
   </sheetData>
@@ -4763,7 +4763,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="n">
         <v>-0.105582</v>
       </c>
@@ -4819,7 +4823,11 @@
           <t>Net proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -4939,7 +4947,11 @@
           <t>Shares issued for cash (net)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>4.762637</v>
       </c>
@@ -5814,7 +5826,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E105" s="5" t="n">
         <v>0.618009</v>
       </c>
@@ -6110,7 +6126,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E115" s="5" t="n">
         <v>-5.407362</v>
       </c>
@@ -6137,7 +6157,11 @@
           <t>Loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -6648,7 +6672,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -6677,7 +6705,11 @@
           <t>Net loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -7865,7 +7897,11 @@
           <t>Loss from discontinued operations 8</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E172" s="5" t="n">
         <v>-0.223629</v>
       </c>
